--- a/T01_bo_prototype/data/experiments.xlsx
+++ b/T01_bo_prototype/data/experiments.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O10"/>
+  <dimension ref="A1:O11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -733,46 +733,46 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>1877</v>
+        <v>1561</v>
       </c>
       <c r="C7" t="n">
-        <v>1560</v>
+        <v>1943</v>
       </c>
       <c r="D7" t="n">
-        <v>1515</v>
+        <v>1492</v>
       </c>
       <c r="E7" t="n">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="F7" t="n">
-        <v>73</v>
+        <v>48</v>
       </c>
       <c r="G7" t="n">
-        <v>100</v>
+        <v>47</v>
       </c>
       <c r="H7" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="I7" t="n">
         <v>1</v>
       </c>
       <c r="J7" t="n">
-        <v>209.4295901789938</v>
+        <v>198.3291538527384</v>
       </c>
       <c r="K7" t="n">
-        <v>207.8623074678697</v>
+        <v>196.7618711416143</v>
       </c>
       <c r="L7" t="n">
-        <v>211.0902995884684</v>
+        <v>199.989863262213</v>
       </c>
       <c r="M7" t="n">
-        <v>191.9237363920258</v>
+        <v>179.4584872935817</v>
       </c>
       <c r="N7" t="n">
-        <v>194.0705402752981</v>
+        <v>181.605291176854</v>
       </c>
       <c r="O7" t="n">
-        <v>190.9915198757946</v>
+        <v>178.5262707773505</v>
       </c>
     </row>
     <row r="8">
@@ -780,99 +780,188 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1561</v>
+        <v>1957</v>
       </c>
       <c r="C8" t="n">
-        <v>1943</v>
+        <v>1466</v>
       </c>
       <c r="D8" t="n">
-        <v>1492</v>
+        <v>1959</v>
       </c>
       <c r="E8" t="n">
-        <v>42</v>
+        <v>83</v>
       </c>
       <c r="F8" t="n">
-        <v>48</v>
+        <v>90</v>
       </c>
       <c r="G8" t="n">
-        <v>47</v>
+        <v>92</v>
       </c>
       <c r="H8" t="n">
-        <v>12</v>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
-      <c r="O8" t="inlineStr"/>
+        <v>26</v>
+      </c>
+      <c r="I8" t="n">
+        <v>1</v>
+      </c>
+      <c r="J8" t="n">
+        <v>218.4665805869455</v>
+      </c>
+      <c r="K8" t="n">
+        <v>220.6367072349362</v>
+      </c>
+      <c r="L8" t="n">
+        <v>207.6473578081142</v>
+      </c>
+      <c r="M8" t="n">
+        <v>193.7407083020466</v>
+      </c>
+      <c r="N8" t="n">
+        <v>197.1957617133417</v>
+      </c>
+      <c r="O8" t="n">
+        <v>198.2110289623278</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2000</v>
+        <v>1730</v>
       </c>
       <c r="C9" t="n">
-        <v>1791</v>
+        <v>1704</v>
       </c>
       <c r="D9" t="n">
-        <v>1633</v>
+        <v>1664</v>
       </c>
       <c r="E9" t="n">
-        <v>45</v>
+        <v>64</v>
       </c>
       <c r="F9" t="n">
-        <v>99</v>
+        <v>83</v>
       </c>
       <c r="G9" t="n">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="H9" t="n">
-        <v>18</v>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
-      <c r="O9" t="inlineStr"/>
+        <v>19</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" t="n">
+        <v>206.1824003623268</v>
+      </c>
+      <c r="K9" t="n">
+        <v>207.0749465147797</v>
+      </c>
+      <c r="L9" t="n">
+        <v>205.3562963361677</v>
+      </c>
+      <c r="M9" t="n">
+        <v>181.9098132264672</v>
+      </c>
+      <c r="N9" t="n">
+        <v>183.2175763872239</v>
+      </c>
+      <c r="O9" t="n">
+        <v>181.6066490777496</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2000</v>
+        <v>1489</v>
       </c>
       <c r="C10" t="n">
-        <v>1412</v>
+        <v>1687</v>
       </c>
       <c r="D10" t="n">
-        <v>1804</v>
+        <v>1835</v>
       </c>
       <c r="E10" t="n">
-        <v>61</v>
+        <v>92</v>
       </c>
       <c r="F10" t="n">
+        <v>57</v>
+      </c>
+      <c r="G10" t="n">
         <v>66</v>
       </c>
-      <c r="G10" t="n">
-        <v>100</v>
-      </c>
       <c r="H10" t="n">
-        <v>16</v>
-      </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
-      <c r="O10" t="inlineStr"/>
+        <v>23</v>
+      </c>
+      <c r="I10" t="n">
+        <v>1</v>
+      </c>
+      <c r="J10" t="n">
+        <v>193.4817220971316</v>
+      </c>
+      <c r="K10" t="n">
+        <v>194.6865929130789</v>
+      </c>
+      <c r="L10" t="n">
+        <v>194.6132011669273</v>
+      </c>
+      <c r="M10" t="n">
+        <v>174.6292573761446</v>
+      </c>
+      <c r="N10" t="n">
+        <v>168.7463640308897</v>
+      </c>
+      <c r="O10" t="n">
+        <v>175.117417181726</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>9</v>
+      </c>
+      <c r="B11" t="n">
+        <v>1549</v>
+      </c>
+      <c r="C11" t="n">
+        <v>1920</v>
+      </c>
+      <c r="D11" t="n">
+        <v>1641</v>
+      </c>
+      <c r="E11" t="n">
+        <v>78</v>
+      </c>
+      <c r="F11" t="n">
+        <v>74</v>
+      </c>
+      <c r="G11" t="n">
+        <v>59</v>
+      </c>
+      <c r="H11" t="n">
+        <v>11</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" t="n">
+        <v>197.9766707500079</v>
+      </c>
+      <c r="K11" t="n">
+        <v>201.1137312791935</v>
+      </c>
+      <c r="L11" t="n">
+        <v>195.4161452768298</v>
+      </c>
+      <c r="M11" t="n">
+        <v>179.7380146882647</v>
+      </c>
+      <c r="N11" t="n">
+        <v>181.2000591236709</v>
+      </c>
+      <c r="O11" t="n">
+        <v>176.411867046571</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/T01_bo_prototype/data/experiments.xlsx
+++ b/T01_bo_prototype/data/experiments.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O11"/>
+  <dimension ref="A1:O21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -963,6 +963,336 @@
         <v>176.411867046571</v>
       </c>
     </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>10</v>
+      </c>
+      <c r="B12" t="n">
+        <v>1754</v>
+      </c>
+      <c r="C12" t="n">
+        <v>1491</v>
+      </c>
+      <c r="D12" t="n">
+        <v>1813</v>
+      </c>
+      <c r="E12" t="n">
+        <v>47</v>
+      </c>
+      <c r="F12" t="n">
+        <v>70</v>
+      </c>
+      <c r="G12" t="n">
+        <v>81</v>
+      </c>
+      <c r="H12" t="n">
+        <v>27</v>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="O12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>11</v>
+      </c>
+      <c r="B13" t="n">
+        <v>1415</v>
+      </c>
+      <c r="C13" t="n">
+        <v>1636</v>
+      </c>
+      <c r="D13" t="n">
+        <v>1796</v>
+      </c>
+      <c r="E13" t="n">
+        <v>100</v>
+      </c>
+      <c r="F13" t="n">
+        <v>56</v>
+      </c>
+      <c r="G13" t="n">
+        <v>88</v>
+      </c>
+      <c r="H13" t="n">
+        <v>27</v>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="O13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>12</v>
+      </c>
+      <c r="B14" t="n">
+        <v>1439</v>
+      </c>
+      <c r="C14" t="n">
+        <v>1478</v>
+      </c>
+      <c r="D14" t="n">
+        <v>1514</v>
+      </c>
+      <c r="E14" t="n">
+        <v>77</v>
+      </c>
+      <c r="F14" t="n">
+        <v>41</v>
+      </c>
+      <c r="G14" t="n">
+        <v>77</v>
+      </c>
+      <c r="H14" t="n">
+        <v>30</v>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="O14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>13</v>
+      </c>
+      <c r="B15" t="n">
+        <v>1463</v>
+      </c>
+      <c r="C15" t="n">
+        <v>1400</v>
+      </c>
+      <c r="D15" t="n">
+        <v>2000</v>
+      </c>
+      <c r="E15" t="n">
+        <v>75</v>
+      </c>
+      <c r="F15" t="n">
+        <v>96</v>
+      </c>
+      <c r="G15" t="n">
+        <v>78</v>
+      </c>
+      <c r="H15" t="n">
+        <v>30</v>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="O15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>14</v>
+      </c>
+      <c r="B16" t="n">
+        <v>1434</v>
+      </c>
+      <c r="C16" t="n">
+        <v>2000</v>
+      </c>
+      <c r="D16" t="n">
+        <v>2000</v>
+      </c>
+      <c r="E16" t="n">
+        <v>100</v>
+      </c>
+      <c r="F16" t="n">
+        <v>40</v>
+      </c>
+      <c r="G16" t="n">
+        <v>88</v>
+      </c>
+      <c r="H16" t="n">
+        <v>30</v>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="O16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>15</v>
+      </c>
+      <c r="B17" t="n">
+        <v>1450</v>
+      </c>
+      <c r="C17" t="n">
+        <v>1400</v>
+      </c>
+      <c r="D17" t="n">
+        <v>2000</v>
+      </c>
+      <c r="E17" t="n">
+        <v>100</v>
+      </c>
+      <c r="F17" t="n">
+        <v>40</v>
+      </c>
+      <c r="G17" t="n">
+        <v>87</v>
+      </c>
+      <c r="H17" t="n">
+        <v>10</v>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
+      <c r="O17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>16</v>
+      </c>
+      <c r="B18" t="n">
+        <v>1473</v>
+      </c>
+      <c r="C18" t="n">
+        <v>2000</v>
+      </c>
+      <c r="D18" t="n">
+        <v>2000</v>
+      </c>
+      <c r="E18" t="n">
+        <v>40</v>
+      </c>
+      <c r="F18" t="n">
+        <v>72</v>
+      </c>
+      <c r="G18" t="n">
+        <v>82</v>
+      </c>
+      <c r="H18" t="n">
+        <v>30</v>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
+      <c r="O18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>17</v>
+      </c>
+      <c r="B19" t="n">
+        <v>1454</v>
+      </c>
+      <c r="C19" t="n">
+        <v>2000</v>
+      </c>
+      <c r="D19" t="n">
+        <v>1412</v>
+      </c>
+      <c r="E19" t="n">
+        <v>100</v>
+      </c>
+      <c r="F19" t="n">
+        <v>40</v>
+      </c>
+      <c r="G19" t="n">
+        <v>78</v>
+      </c>
+      <c r="H19" t="n">
+        <v>30</v>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
+      <c r="O19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>18</v>
+      </c>
+      <c r="B20" t="n">
+        <v>1430</v>
+      </c>
+      <c r="C20" t="n">
+        <v>1702</v>
+      </c>
+      <c r="D20" t="n">
+        <v>2000</v>
+      </c>
+      <c r="E20" t="n">
+        <v>100</v>
+      </c>
+      <c r="F20" t="n">
+        <v>100</v>
+      </c>
+      <c r="G20" t="n">
+        <v>94</v>
+      </c>
+      <c r="H20" t="n">
+        <v>30</v>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
+      <c r="O20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>19</v>
+      </c>
+      <c r="B21" t="n">
+        <v>1441</v>
+      </c>
+      <c r="C21" t="n">
+        <v>1708</v>
+      </c>
+      <c r="D21" t="n">
+        <v>1840</v>
+      </c>
+      <c r="E21" t="n">
+        <v>40</v>
+      </c>
+      <c r="F21" t="n">
+        <v>44</v>
+      </c>
+      <c r="G21" t="n">
+        <v>89</v>
+      </c>
+      <c r="H21" t="n">
+        <v>10</v>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
+      <c r="O21" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/T01_bo_prototype/data/experiments.xlsx
+++ b/T01_bo_prototype/data/experiments.xlsx
@@ -988,122 +988,178 @@
       <c r="H12" t="n">
         <v>27</v>
       </c>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
-      <c r="O12" t="inlineStr"/>
+      <c r="I12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J12" t="n">
+        <v>203.7297882493973</v>
+      </c>
+      <c r="K12" t="n">
+        <v>204.8647296758605</v>
+      </c>
+      <c r="L12" t="n">
+        <v>204.6943878246397</v>
+      </c>
+      <c r="M12" t="n">
+        <v>186.3432046594921</v>
+      </c>
+      <c r="N12" t="n">
+        <v>184.7965349019922</v>
+      </c>
+      <c r="O12" t="n">
+        <v>185.9217262448445</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>1415</v>
+        <v>1429</v>
       </c>
       <c r="C13" t="n">
-        <v>1636</v>
+        <v>1667</v>
       </c>
       <c r="D13" t="n">
-        <v>1796</v>
+        <v>1704</v>
       </c>
       <c r="E13" t="n">
-        <v>100</v>
+        <v>70</v>
       </c>
       <c r="F13" t="n">
         <v>56</v>
       </c>
       <c r="G13" t="n">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="H13" t="n">
-        <v>27</v>
-      </c>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
-      <c r="O13" t="inlineStr"/>
+        <v>25</v>
+      </c>
+      <c r="I13" t="n">
+        <v>1</v>
+      </c>
+      <c r="J13" t="n">
+        <v>197.1967106590786</v>
+      </c>
+      <c r="K13" t="n">
+        <v>201.1733749782489</v>
+      </c>
+      <c r="L13" t="n">
+        <v>200.7682955930769</v>
+      </c>
+      <c r="M13" t="n">
+        <v>172.1527404410832</v>
+      </c>
+      <c r="N13" t="n">
+        <v>172.7897531381268</v>
+      </c>
+      <c r="O13" t="n">
+        <v>172.1015090923459</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1439</v>
+        <v>1454</v>
       </c>
       <c r="C14" t="n">
-        <v>1478</v>
+        <v>1400</v>
       </c>
       <c r="D14" t="n">
-        <v>1514</v>
+        <v>1400</v>
       </c>
       <c r="E14" t="n">
-        <v>77</v>
+        <v>100</v>
       </c>
       <c r="F14" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G14" t="n">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="H14" t="n">
         <v>30</v>
       </c>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
-      <c r="O14" t="inlineStr"/>
+      <c r="I14" t="n">
+        <v>1</v>
+      </c>
+      <c r="J14" t="n">
+        <v>197.7321127119187</v>
+      </c>
+      <c r="K14" t="n">
+        <v>200.8910229284299</v>
+      </c>
+      <c r="L14" t="n">
+        <v>199.9773583153807</v>
+      </c>
+      <c r="M14" t="n">
+        <v>176.6788232117189</v>
+      </c>
+      <c r="N14" t="n">
+        <v>179.3632822567711</v>
+      </c>
+      <c r="O14" t="n">
+        <v>170.8902791588299</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1463</v>
+        <v>1456</v>
       </c>
       <c r="C15" t="n">
-        <v>1400</v>
+        <v>1991</v>
       </c>
       <c r="D15" t="n">
         <v>2000</v>
       </c>
       <c r="E15" t="n">
-        <v>75</v>
+        <v>57</v>
       </c>
       <c r="F15" t="n">
-        <v>96</v>
+        <v>40</v>
       </c>
       <c r="G15" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H15" t="n">
         <v>30</v>
       </c>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
-      <c r="O15" t="inlineStr"/>
+      <c r="I15" t="n">
+        <v>1</v>
+      </c>
+      <c r="J15" t="n">
+        <v>203.2860789569249</v>
+      </c>
+      <c r="K15" t="n">
+        <v>188.5708135464585</v>
+      </c>
+      <c r="L15" t="n">
+        <v>200.6800012029791</v>
+      </c>
+      <c r="M15" t="n">
+        <v>174.7823566026957</v>
+      </c>
+      <c r="N15" t="n">
+        <v>178.528194992256</v>
+      </c>
+      <c r="O15" t="n">
+        <v>175.730332669708</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1434</v>
+        <v>1456</v>
       </c>
       <c r="C16" t="n">
-        <v>2000</v>
+        <v>1400</v>
       </c>
       <c r="D16" t="n">
         <v>2000</v>
@@ -1112,61 +1168,89 @@
         <v>100</v>
       </c>
       <c r="F16" t="n">
-        <v>40</v>
+        <v>92</v>
       </c>
       <c r="G16" t="n">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="H16" t="n">
         <v>30</v>
       </c>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
-      <c r="O16" t="inlineStr"/>
+      <c r="I16" t="n">
+        <v>1</v>
+      </c>
+      <c r="J16" t="n">
+        <v>199.8923685871671</v>
+      </c>
+      <c r="K16" t="n">
+        <v>194.8673867719764</v>
+      </c>
+      <c r="L16" t="n">
+        <v>193.0853382782095</v>
+      </c>
+      <c r="M16" t="n">
+        <v>165.7985332041902</v>
+      </c>
+      <c r="N16" t="n">
+        <v>173.5137484289648</v>
+      </c>
+      <c r="O16" t="n">
+        <v>178.3162640375462</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>1450</v>
+        <v>1445</v>
       </c>
       <c r="C17" t="n">
-        <v>1400</v>
+        <v>1578</v>
       </c>
       <c r="D17" t="n">
         <v>2000</v>
       </c>
       <c r="E17" t="n">
-        <v>100</v>
+        <v>61</v>
       </c>
       <c r="F17" t="n">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="G17" t="n">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H17" t="n">
         <v>10</v>
       </c>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
-      <c r="O17" t="inlineStr"/>
+      <c r="I17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J17" t="n">
+        <v>193.2215155105247</v>
+      </c>
+      <c r="K17" t="n">
+        <v>194.7044914301429</v>
+      </c>
+      <c r="L17" t="n">
+        <v>198.6959496495031</v>
+      </c>
+      <c r="M17" t="n">
+        <v>172.6366371309234</v>
+      </c>
+      <c r="N17" t="n">
+        <v>175.7857456281819</v>
+      </c>
+      <c r="O17" t="n">
+        <v>176.6308678848574</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1473</v>
+        <v>1446</v>
       </c>
       <c r="C18" t="n">
         <v>2000</v>
@@ -1175,123 +1259,179 @@
         <v>2000</v>
       </c>
       <c r="E18" t="n">
+        <v>100</v>
+      </c>
+      <c r="F18" t="n">
         <v>40</v>
       </c>
-      <c r="F18" t="n">
-        <v>72</v>
-      </c>
       <c r="G18" t="n">
-        <v>82</v>
+        <v>99</v>
       </c>
       <c r="H18" t="n">
-        <v>30</v>
-      </c>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
-      <c r="O18" t="inlineStr"/>
+        <v>17</v>
+      </c>
+      <c r="I18" t="n">
+        <v>1</v>
+      </c>
+      <c r="J18" t="n">
+        <v>195.7563781789614</v>
+      </c>
+      <c r="K18" t="n">
+        <v>199.4328997347421</v>
+      </c>
+      <c r="L18" t="n">
+        <v>200.6586116421538</v>
+      </c>
+      <c r="M18" t="n">
+        <v>177.3346865109985</v>
+      </c>
+      <c r="N18" t="n">
+        <v>179.6954595735697</v>
+      </c>
+      <c r="O18" t="n">
+        <v>173.0863531348322</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1454</v>
+        <v>1429</v>
       </c>
       <c r="C19" t="n">
-        <v>2000</v>
+        <v>1421</v>
       </c>
       <c r="D19" t="n">
-        <v>1412</v>
+        <v>1400</v>
       </c>
       <c r="E19" t="n">
-        <v>100</v>
+        <v>41</v>
       </c>
       <c r="F19" t="n">
         <v>40</v>
       </c>
       <c r="G19" t="n">
-        <v>78</v>
+        <v>64</v>
       </c>
       <c r="H19" t="n">
         <v>30</v>
       </c>
-      <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
-      <c r="O19" t="inlineStr"/>
+      <c r="I19" t="n">
+        <v>1</v>
+      </c>
+      <c r="J19" t="n">
+        <v>200.3979197178366</v>
+      </c>
+      <c r="K19" t="n">
+        <v>198.1094261872576</v>
+      </c>
+      <c r="L19" t="n">
+        <v>195.4742178115586</v>
+      </c>
+      <c r="M19" t="n">
+        <v>169.9029361008888</v>
+      </c>
+      <c r="N19" t="n">
+        <v>167.9997978619284</v>
+      </c>
+      <c r="O19" t="n">
+        <v>173.739576544396</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>1430</v>
+        <v>1449</v>
       </c>
       <c r="C20" t="n">
-        <v>1702</v>
+        <v>1400</v>
       </c>
       <c r="D20" t="n">
-        <v>2000</v>
+        <v>1457</v>
       </c>
       <c r="E20" t="n">
         <v>100</v>
       </c>
       <c r="F20" t="n">
-        <v>100</v>
+        <v>40</v>
       </c>
       <c r="G20" t="n">
-        <v>94</v>
+        <v>79</v>
       </c>
       <c r="H20" t="n">
-        <v>30</v>
-      </c>
-      <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
-      <c r="O20" t="inlineStr"/>
+        <v>10</v>
+      </c>
+      <c r="I20" t="n">
+        <v>1</v>
+      </c>
+      <c r="J20" t="n">
+        <v>196.3228934043493</v>
+      </c>
+      <c r="K20" t="n">
+        <v>194.2296231053013</v>
+      </c>
+      <c r="L20" t="n">
+        <v>199.6414443947565</v>
+      </c>
+      <c r="M20" t="n">
+        <v>171.0176898558085</v>
+      </c>
+      <c r="N20" t="n">
+        <v>180.3828803999066</v>
+      </c>
+      <c r="O20" t="n">
+        <v>177.1134697607365</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>1441</v>
+        <v>1483</v>
       </c>
       <c r="C21" t="n">
-        <v>1708</v>
+        <v>1400</v>
       </c>
       <c r="D21" t="n">
-        <v>1840</v>
+        <v>2000</v>
       </c>
       <c r="E21" t="n">
         <v>40</v>
       </c>
       <c r="F21" t="n">
-        <v>44</v>
+        <v>98</v>
       </c>
       <c r="G21" t="n">
-        <v>89</v>
+        <v>69</v>
       </c>
       <c r="H21" t="n">
-        <v>10</v>
-      </c>
-      <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr"/>
-      <c r="N21" t="inlineStr"/>
-      <c r="O21" t="inlineStr"/>
+        <v>30</v>
+      </c>
+      <c r="I21" t="n">
+        <v>1</v>
+      </c>
+      <c r="J21" t="n">
+        <v>197.4226521824281</v>
+      </c>
+      <c r="K21" t="n">
+        <v>201.5149625664967</v>
+      </c>
+      <c r="L21" t="n">
+        <v>199.780298932339</v>
+      </c>
+      <c r="M21" t="n">
+        <v>173.6257697928824</v>
+      </c>
+      <c r="N21" t="n">
+        <v>177.4966833237406</v>
+      </c>
+      <c r="O21" t="n">
+        <v>171.1301124013759</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
